--- a/llm-classifier/results/corpus.xlsx
+++ b/llm-classifier/results/corpus.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G228"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7024,7 +7024,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025S01</t>
+          <t>2024S01</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7053,7 +7053,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025S02</t>
+          <t>2024S02</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -7082,7 +7082,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025S03</t>
+          <t>2024S03</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025S04</t>
+          <t>2024S04</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -7141,7 +7141,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025S05</t>
+          <t>2024S05</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7170,7 +7170,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025S06</t>
+          <t>2024S06</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7203,7 +7203,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025S07</t>
+          <t>2024S07</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7233,7 +7233,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025S08</t>
+          <t>2024S08</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7263,7 +7263,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025S09</t>
+          <t>2024S09</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7293,7 +7293,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025S10</t>
+          <t>2024S10</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7322,7 +7322,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025S11</t>
+          <t>2024S11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7351,7 +7351,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025S12</t>
+          <t>2024S12</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7380,7 +7380,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025S13</t>
+          <t>2024S13</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7412,7 +7412,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025S14</t>
+          <t>2024S14</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7441,7 +7441,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025S15</t>
+          <t>2024S15</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7471,7 +7471,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025S16</t>
+          <t>2024S16</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7500,7 +7500,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025S17</t>
+          <t>2024S17</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7529,7 +7529,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025S18</t>
+          <t>2024S18</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7559,7 +7559,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025S19</t>
+          <t>2024S19</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7588,7 +7588,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025S20</t>
+          <t>2024S20</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7617,7 +7617,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025S21</t>
+          <t>2024S21</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7646,7 +7646,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025S22</t>
+          <t>2024S22</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7676,7 +7676,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025S23</t>
+          <t>2024S23</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7707,7 +7707,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025S24</t>
+          <t>2024S24</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7737,7 +7737,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025S25</t>
+          <t>2024S25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025S26</t>
+          <t>2024S26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7797,7 +7797,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025S27</t>
+          <t>2024S27</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7828,7 +7828,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025S28</t>
+          <t>2024S28</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7858,7 +7858,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025S29</t>
+          <t>2024S29</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025S30</t>
+          <t>2024S30</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7918,7 +7918,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025S31</t>
+          <t>2024S31</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7947,7 +7947,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025S32</t>
+          <t>2024S32</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7976,7 +7976,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025S33</t>
+          <t>2024S33</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8005,7 +8005,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025S34</t>
+          <t>2024S34</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8037,7 +8037,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025S35</t>
+          <t>2024S35</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025S36</t>
+          <t>2024S36</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8095,7 +8095,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025S37</t>
+          <t>2024S37</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8124,7 +8124,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025S38</t>
+          <t>2024S38</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8154,7 +8154,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025S39</t>
+          <t>2024S39</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025S40</t>
+          <t>2024S40</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8212,7 +8212,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025S41</t>
+          <t>2024S41</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025S42</t>
+          <t>2024S42</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8270,7 +8270,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025S43</t>
+          <t>2024S43</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8309,7 +8309,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025S44</t>
+          <t>2024S44</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8332,6 +8332,615 @@
       <c r="G228" t="inlineStr">
         <is>
           <t>seguimiento_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2025S01</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SISTEMA DE IDENTIFICACION DE INSTRUMENTOS MUSICALES DE LA REGION ANDINA USANDO TECNICAS DE MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Identificador, Intrumentos musicales, Musica andina, Inteligencia Artificial, Machine Learning</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Este proyecto presenta el desarrollo de un sistema de identificación de instrumentos musicales específicos de la región andina utilizando diferentes técnicas de Machine Learning. El sistema propuesto emplea algoritmos de clasificación para analizar y categorizar sonidos musicales, facilitando la identificación automática de instrumentos como la quena, el charango, la zampoña y el bombo andino, entre otros adicionales. Se recolectarán datos acústicos de diversas fuentes y se procesarán para extraer características relevantes que alimenten los modelos de aprendizaje automático.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025S02</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA EN GESTION INTEGRAL DE FACTURACIÓN DIGITAL PARA PEQUENOS PRESTADORES DE SERVICIOS PÚBLICOS</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Sistema de facturación, Servicios públicos, Prototipo wireframes, Prototipo mockups</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Este documento describe la implementación de un sistema de facturación digital para pequeños prestadores de servicios públicos, específicamente en el contexto de acueductos de pequeña escala. La necesidad de optimizar y automatizar este proceso se debe a las limitaciones y deficiencias actuales en la gestión financiera de estos sistemas, que afectan la precisión, eficiencia y transparencia en la administración de los mismos. El objetivo del prototipo logrado es proporcionar un sistema de facturación digital adaptado a las particularidades y necesidades específicas de las pequeñas entidades que prestan servicios públicos. El prototipo proporciona funcionalidades clave para agilizar la generación de facturas, facilitar la gestión de usuarios y mejorar la transparencia en la administración financiera, permitiendo obtener datos específicos que pue den servir como base de datos informativa para la entidad. La creación del prototipo se realizó mediante un enfoque ágil, utilizando instrumentos y tecnologías actuales para el diseño y desarrollo del sistema. Se desarrollaron wireframes y mockups que permitieron dar una percepción clara del sistema al usuario final. El prototipo fue sometido a pruebas que confirmaron su funcionalidad y eficiencia en el procesamiento de datos y carga masiva de información. Los resultados obtenidos muestran que el prototipo tiene una buena aceptación y su procesamiento es eficiente. Se espera que el sistema desarrollado contribuya significativamente a la mejora de la gestión financiera en pequeños acueductos, ofreciendo una solución integral y adaptada a las necesidades de la entidad que lo desee implementar. La implementación de este sistema puede tener un impacto positivo en la eficiencia y transparencia de la gestión financiera de estos sistemas.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025S03</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SISTEMATIZACIÓN DE LA GESTIÓN ADMINISTRATIVA DE INFORMACIÓN Y LÓGICA DE NEGOCIO PARA LA RECOLECCIÓN DE DESECHOS EN LA EMPRESA AGUAS DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Desarrollo de software, sistematización, gestión administrativa, operación de negocios</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>En este documento se aborda la profundización respecto a la necesidad de un sistema integral alrededor del gestionamiento y la administración de la información de las operaciones de negocio en la empresa Aguas de la Sabana de Bogotá S.A E.S.P., una empresa privada prestadora de los servicios de acueducto, alcantarillado y aseo, que contribuye al desarrollo de los municipios de Cota, Funza y Tenjo. El objetivo es mejorar la administración de acuerdos y tarifas según norma CRA 151 del 2001, Anexo 8, la gestión de clientes y técnicos/operarios registrados, la relación de información de rutas, micro rutas y clientes correspondientes a las mismas, y la gestión de los recursos operacionales como los camiones de recolección, entre otros. Contribuyendo así a la mejora de la experiencia tanto del administrador como de los operarios y al cumplimiento normativo de la empresa.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2025S04</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE SISTEMA DE RECOMENDACIÓN PARA ELECCIÓN DE VEHÍCULO TIPO MOTOCICLETA BASADO EN FILTRADO COLABORATIVO</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Inteligencia Artificial, Sistemas de recomendación, Filtrado Colaborativo, Características específicas, Motocicletas</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>La elección de una motocicleta es un proceso complejo que puede resultar abrumador para los usuarios debido a la diversidad de opciones disponibles y las diferentes necesidades y preferencias individuales. La propuesta de un sistema de recomendación de motocicletas buscó abordar este desafío al proporcionar orientación personalizada y precisa a los usuarios en su búsqueda del vehículo perfecto. Este sistema se implementó utilizando una metodología basada en el análisis de datos, el aprendizaje automático y el filtrado colaborativo. A través de estas tecnologías, se comprendieron las preferencias de los usuarios y se sugirieron motocicletas que se adaptaran mejor a sus necesidades y gustos individuales. De esta manera, el sistema ofreció recomendaciones personalizadas que se alinearon específicamente con las características y preferencias únicas de cada usuario, mejorando significativamente la precisión y relevancia de las sugerencias. Los resultados obtenidos mostraron una mejora considerable en la satisfacción del usuario al reducir el tiempo y esfuerzo necesarios para encontrar una motocicleta adecuada, adaptándose de forma precisa a las necesidades personales de cada individuo.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025S05</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PRONUNCIAPP: PROTOTIPO DE APLICACION WEB PARA LA MEJORA DE LA PRONUNCIACIÓN DEL INGLÉS EN LOS ESTUDIANTES DE LA CARRERA DE INGENIERÍA DE SISTEMAS DE LA UNIVERSIDAD DEL VALLE, SEDE TULUÁ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Prototipo aplicación web, inteligencia artificial, idioma ingles, PronunciApp</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PronunciApp es un prototipo de aplicación web desarrollado como proyecto de grado para proporcionar una mejora sobre la pronunciación del idioma inglés a estudiantes de Ingeniería de Sistemas de la Universidad del Valle, sede Tuluá. El sistema implementado permite a los usuarios grabar su voz al repetir palabras en inglés, las cuales son analizadas utilizando tecnologías de reconocimiento de voz para generar retroalimentación sobre aspectos de la pronunciación. La aplicación se desarrolló utilizando Angular 19 para la interfaz de usuario, FastAPI para el backend, y se desplegó en la plataforma Azure. El proceso de desarrollo siguió la metodología Scrumban a lo largo de 40 sprints, aplicando principios de diseño UX/UI para crear una herramienta que permite la práctica de pronunciación mediante el análisis de grabaciones de audio.</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025S06</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CREACIÓN DE MÓDULOS INTERACTIVOS PARA EL DESARROLLO CONTINUO DE LA ORATORIA Y EL PENSAMIENTO CRÍTICO DE TEXTOS EN EL PROTOTIPO DE ENSEÑANZA DE HABILIDADES BLANDAS</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Procesamiento del lenguaje natural, Comunicación efectiva, pensamiento crítico, plataforma educativa, habilidades blandas, inteligencia artificial.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Con frecuencia, se observa que la importancia de ciertas habilidades es pasada por alto en los programas de formación, a pesar de su relevancia en el mercado laboral actual y futuro. La comunicación efectiva y el pensamiento crítico constituyen pilares importantes para que los ingenieros puedan abordar los desafíos venideros y ofrecer soluciones de calidad a sus clientes. El descuido de estas habilidades en la formación de ingenieros puede ocasionar consecuencias negativas tanto en su desempeño profesional como en el éxito de los proyectos que emprendan. Este proyecto se centró en crear y poner en marcha módulos interactivos para el desarrollo de habilidades de oratoria y pensamiento crítico dirigidos específicamente a los estudiantes de ingeniería de sistemas de la Universidad del Valle en Tuluá. Se implementaron estrategias educativas que incluyen el uso de inteligencia artificial y procesamiento de lenguaje natural para proporcionar retroalimentación personalizada a los estudiantes. Al impulsar el desarrollo de estas habilidades, las instituciones educativas pudieron contribuir de manera significativa a la formación de profesionales versátiles y capacitados que estuvieran mejor preparados para enfrentar los desafíos venideros con mayor confianza y competencia.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025S07</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN SOFTWARE PARA LA PREDICCIÓN DE VENTAS FUTURAS UTILIZANDO MODELOS PREDICTIVOS.</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Aplicativo web, pronostico en ventas, futuras, modelos predictivos, inteligencia artificial, PYMES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>En este trabajo de grado se aborda el desarrollo de un aplicativo de software para el pronóstico de ventas utilizando algoritmos de inteligencia artificial. El problema evidenciado es la carencia de una herramienta que permita a las pequeñas y medianas empresas (PYMES) tomar mejores decisiones de manera informada para la gestión de su inventario ya que para una empresa tener una buena gestión del inventario es crucial ya que las ventas pueden fluctuar de una manera poco predecible lo que puede llevar a pérdidas eco nómicas por tener poco o demasiado inventario. Las pequeñas empresas, pueden enfrentar más dificultades en la gestión del inventario, lo cual puede resultar poco eficiente debido a que suelen realizar esta gestión de manera manual y sin un estudio previo. El objetivo principal de este trabajo de grado es crear una herramienta capaz de generar pronósticos de ventas precisos a partir de datos históricos, integrando modelos predicti vos entrenados con técnicas de machine learning. Para ello, se implementaron y evaluaron tres modelos distintos: una red neuronal LSTM (Long Short-Term Memory), un modelo de soporte vectorial para regresión (SVM) con distintos kernels, y un modelo estadístico SARIMA (Seasonal Autoregressive Integrated Moving Average). Las métricas utilizadas para evaluar el desempeño de los modelos fueron el Error Cuadrático Medio (MSE), el Error Absoluto Medio (MAE) y el Error Porcentual Absoluto Medio (MAPE). El proyecto fue desarrollado bajo la metodología ágil Scrum, adaptada para un entorno de trabajo individual</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025S08</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE APLICACIÓN WEB COMO HERRAMIENTA DE APOYO PARA LA EVALUACIÓN DE COMPETENCIAS EN PENSAMIENTO COMPUTACIONAL</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Metodologías educativas, pensamiento computacional, evaluación de competencias, aplicación web</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>El pensamiento computacional se ha consolidado como una habilidad fundamental para el siglo XXI, ya que permite a los individuos comprender y participar activamente en el mundo digital. En el caso de los jóvenes, su desarrollo aporta beneficios significativos en múltiples dimensiones. En primer lugar, promueve el razonamiento lógico y el pensamiento crítico, al requerir que los estudiantes aborden problemas de manera sistemática y estructurada, estas habilidades resultan clave tanto para el desempeño académico como para la toma de decisiones en la vida cotidiana. Además, estimula la creatividad y la innovación, al incentivar la búsqueda de soluciones originales a diversos retos, capacidades especialmente valoradas en el contexto actual. Asimismo, el pensamiento computacional prepara a los jóvenes para enfrentar los desafíos del mercado laboral, especialmente en áreas relacionadas con la ciencia, la tecnología, la ingeniería y las matemáticas, donde estas competencias son cada vez más demandadas. Reconociendo su relevancia, se han propuesto múltiples metodologías para enseñar pensamiento computacional, cada una con distintos enfoques y estrategias de evaluación. Sin embargo, las investigaciones evidencian deficiencias en los métodos de evaluación existentes, lo que dificulta validar de forma efectiva el aprendizaje de estas competencias. Ante esta problemática, el presente trabajo propone el desarrollo de una aplicación web parametrizable, orientada a evaluar las competencias en pensamiento computacional de estudiantes de educación secundaria. La solución se fundamentará en un modelo de evaluación integral que combine enfoques formales e informales, haciendo uso de rúbricas para valorar el desempeño de los estudiantes en tareas específicas relacionadas con el pensamiento computacional.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025S09</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE PRUEBAS UNITARIAS PARA EL COMPONENTE FRONT-END DEL SOFTWARE ACADEMIAPP PARA LA EMPRESA WEBCLOSTER SAS</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Desarrollo de software Scrum, pruebas unitarias, gestión acádemica, gestión administrativa, AcademiApp</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Cada vez es más crucial para las universidades sistematizar la gestión tanto administrativa como académica. Varias compañías de software han identificado esta necesidad y han entrado en este mercado, entre ellas Webcloster S.A.S. Webcloster S.A.S. es una empresa que se dedica al desarrollo de software que simplifica la dirección y administración de operaciones tanto empresariales como personales, y ha decidido crear un programa llamado AcademiApp para la gestión académica y administrativa. Este programa consiste en una aplicación en línea que facilita la administración de datos, la consulta de horarios disponibles de las aulas, la evaluación de desempeños, entre otras funciones. Para este proyecto se empleará una metodología de investigación aplicada y, adicionalmente, se utilizará la metodología ágil Scrum. Con lo mencionado anteriormente, se espera desarrollar pruebas y realizar el mantenimiento de los módulos asignados para AcademiApp.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2025S10</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>PROTOTIPO WEB COMO SOPORTE PARA LA ENSEÑANZA DE INGLÉS A TRAVÉS DE LA GAMIFICACIÓN Y ALGORITMOS DE PROCESAMIENTO DEL LENGUAJE NATURAL</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Lenguaje natural, gamificación, aprendizaje, habla en ingles, inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>El presente proyecto desarrolló un prototipo web diseñado para mejorar la habilidad del habla en inglés mediante el uso de técnicas de Procesamiento del Lenguaje Natural (PLN) y gamificación. Se aborda la creciente necesidad de herramientas educativas efectivas que involucren a los estudiantes de manera activa y atractiva. El sistema proporciona ejercicios interactivos y elementos de gamificación para motivar a los usuarios a practicar y mejorar su comprensión al momento de hablar en inglés. El enfoque que tiene el sistema aporta al estudiante una herramienta con IA centralizada en distintos algoritmos de PLN con el fin de que el estudiante obtenga un apoyo en el proceso de aprendizaje y que, con ayuda de estos modelos matemáticos, pueda mejorar su fluidez al momento de comunicarse en inglés.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2025S11</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SOFTWARE WEB PARA EL ANÁLISIS Y EVALUACIÓN DE LA EXPOSICIÓN DE DATOS SENSIBLES Y NO SENSIBLES EN LA RED SOCIAL INSTAGRAM APLICADA EN LA UNIVERSIDAD DEL VALLE SEDE TULUÁ</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Procesamiento de Lenguaje Natural, Web Scraping, campus universitario, privacidad de datos, redes sociales.</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>En esta propuesta de trabajo de grado se busca la implementación de un prototipo de software web para capturar la información de texto de las redes sociales (web Scraping o API web scraper) y poder identificar el nivel de exposición de los datos personales sensibles y no sensibles en los campus universitarios, con este proyecto, se quiere motivar a otras entidades educativas a adoptar un enfoque similar, donde el factor clave es promover una cultura ge neral de privacidad y seguridad en línea en todas las comunidades universitarias. Asimismo, se espera formar un futuro digital donde la protección de datos personales sea uno de los pi lares fundamentales, garantizando así un mejor ambiente universitario tanto confiable como respetuoso para todos los miembros que la componen. El presente proyecto constituye una posibilidad hacia la creación de entornos universita rios más seguros y respetuosos de la privacidad. Destacando el papel crucial que la tecnología desempeña como aliada en la protección de los derechos individuales y colectivos, con la aspiración a transformar no solo el entorno académico universitario, sino también a que sirva como ejemplo para otras instituciones educativas en Colombia. El trabajo pretende usar para su desarrollo, las técnicas de procesamiento de lenguaje natural y las tecnologías de trata miento de datos teniendo en cuenta la normatividad de la privacidad de datos.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025S12</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DISEÑO DE UN FORMULARIO WEB PARA LA MEJORA DEL PROCESO DE ONBOARDING Y VALIDACIÓN DE IDENTIDAD EN TRUORA MODALIDAD PASANTÍA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Lenguaje Golang, MOAT, formulario web, constructor digital</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Este documento detalla el diseño e implementación de un constructor de formularios web en Truora, una empresa tecnológica dedicada a la validación de identidad digital y prevención de fraude. Se identificó la necesidad de esta herramienta debido a que los clientes debían recurrir a proveedores externos para la creación de formularios, lo que impedía a Truora centralizar la captura de información valiosa para el perfilamiento de usuarios. El proyecto se enmarca en la estrategia de Truora para 2024, buscando consolidar su posición como proveedor integral. El alcance incluyo todas las etapas de desarrollo del software, desde el levantamiento detallado de requisitos, el diseño de la arquitectura y la base de datos (utilizando AWS y DynamoDB), hasta el desarrollo del constructor de formularios web con tecnologías como Go (Golang) para el backend y Vue.js 3, TypeScript, Flowbite y Tailwind CSS para el frontend. Se siguió una metodología Scrumban, con colaboración cercana con el equipo de producto y UI/UX. Se desarrolló un Form Builder que permite la creación de secciones y preguntas con diversos tipos de input, reordenamiento de campos y validaciones configurables. Se estableció un flujo para el almacenamiento y consulta de respuestas, visibles en el dashboard de Truora. La validación del funcionamiento e integración se realizó a través de pruebas unitarias y funcionales, tanto en el frontend como en el backend, asegurando la compatibilidad con los sistemas existentes de Truora. Finalmente, se procedió al despliegue y monitoreo en el entorno de producción de AWS.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2025S13</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE APLICACIÓN WEB PARA LA GESTIÓN DE PROYECTOS ÁGILES EN DESARROLLO DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Aplicación web, gestión de proyectos, SCRUM, Kanban, código abierto.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>En el entorno actual del desarrollo de software, la implementación efectiva de metodologías agiles resulta fundamental para el éxito de los proyectos. Sin embargo, muchas de las herramientas existentes presentan limitaciones en sus versiones gratuitas, lo que afecta especialmente a estudiantes y desarrolladores independientes con recursos limitados. En respuesta a esta problemática, se desarrolló una aplicación web de gestión de proyectos ágil, enfocada en ofrecer una solución gratuita, accesible y funcional. La plataforma permitió la creación y gestión de tableros Kanban, la generación de in formes del backlog, la integración de roles como Product Owner, Scrum Master y Team Member, y la creación de equipos. Además, incluyó funcionalidades como chat integrado, Planning Poker y una interfaz responsive adaptable a distintos dispositivos. El sistema fue diseñado bajo principios de usabilidad y escalabilidad, y se validó mediante pruebas funcionales. Esta herramienta demostró ser una alternativa eficaz frente a soluciones comerciales, permitiendo a equipos agiles mejorar su productividad y coordinación sin restricciones de acceso ni costo. Adicionalmente, la aplicación podría representar una herramienta valiosa en el entorno académico, especialmente en programas como Ingeniería de Sistemas, donde su uso puede ser integrado en cursos relacionados con el desarrollo de software, metodologías agiles o trabajo colaborativo.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025S14</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA DE RECONOCIMIENTO DE GESTOS DE MANO EN TIEMPO REAL PARA LA INTERACCIÓN HUMANO-COMPUTADORA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Interación humano maquína, sistema en tiempo real, reconocimiento de gestos, visión por computador, seguimiento, accesibilidad, clasificación.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>El presente trabajo se centró en el desarrollo de GestOS, un prototipo de reconocimiento de gestos de mano en tiempo real orientado a mejorar la interacción humano-computadora. Su propósito fue ofrecer una alternativa más accesible e inclusiva a los métodos tradicionales de entrada, como el teclado y el mouse, beneficiando tanto a personas con discapacidades como a quienes buscan nuevas formas de interacción. GestOS se construyó con una arquitectura modular compuesta por cuatro capas: presentación (React, TypeScript y Tailwind CSS), aplicación (Electron y Node.js), lógica de negocio (Python, MediaPipe y OpenCV) y acceso al sistema (PyAutoGUI, pynput y otras librerías). Este diseño permitió mantener una estructura escalable, estable y de fácil mantenimiento. El sistema emplea un enfoque híbrido que combina el análisis de puntos clave de la mano con modelos de aprendizaje automático, logrando reconocer siete gestos principales y algunos adicionales con una precisión cercana al 90%. Para evaluar su funcionamiento, se realizaron pruebas funcionales, de rendimiento y de accesibilidad con 43 usuarios, basadas en las normas WCAG 2.1 (nivel AA). Los resultados fueron positivos, aunque se identificaron áreas de mejora, como el rendimiento en condiciones de baja iluminación y la personalización de gestos. GestOS demuestra que la visión artificial puede contribuir significativamente a crear interfaces más naturales e inclusivas. A futuro, se plantea mejorar la precisión, la velocidad de respuesta y permitir el entrenamiento personalizado de gestos, fortaleciendo así la accesibilidad tecnológica.</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025S15</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PLUGIN PARA LA GESTIÓN DE AMBIENTACIÓN EN ESCENARIOS DE VIDEOJUEGOS UTILIZANDO COMPUTACIÓN EMOCIONAL</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Interacción humano computadora, videojuegos, experiencia emocional, Prototipo integrado en Unity, computación emocional.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Este trabajo de grado tuvo como objetivo desarrollar un plugin innovador para la gestión emocional de la ambientación en videojuegos, basado en los principios de la computación emocional. En los videojuegos actuales, la ambientación influye directamente en la experiencia emocional, la inmersión y la toma de decisiones del jugador. Por ello, se propuso una herramienta capaz de modificar dinámicamente elementos ambientales, especialmente la iluminación, según las emociones del usuario, generando experiencias más personalizadas e inmersivas. Se construyó un prototipo funcional integrado en Unity, diseñado con un enfoque modular y ligero para facilitar su integración en distintos proyectos sin afectar el rendimiento. La validación se realizó mediante una evaluación con usuarios, quienes visualizaron un video demostrativo y respondieron una encuesta sobre su percepción emocional. Los resultados mostraron que la mayoría identificó correctamente las atmósferas emocionales basadas en la iluminación y valoró positivamente su impacto en la narrativa y la experiencia de juego. El proyecto demostró que es posible modular la experiencia emocional del jugador mediante iluminación controlada, sin alterar la arquitectura ni la narrativa explícita. Además, evidenció que las emociones básicas como alegría y tristeza se interpretan con mayor consistencia, mientras que las más complejas requieren mayor contextualización. Finalmente, se concluyó que la iluminación puede actuar como un canal narrativo autónomo, capaz de evocar emociones y enriquecer la experiencia del jugador, aportando así al avance del campo de la computación emocional aplicada a los videojuegos.</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025S16</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>APLICACIÓN WEB DE ATENCIÓN PARA CONSULTAS DE PROCEDIMIENTOS ADMINISTRATIVOS Y PREGUNTAS FRECUENTES CON INTEGRACIÓN DE UN CHATBOT</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Procesamiento Lenguaje Natural, chatbot, inteligencia artificial, procedimientos administrativos.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>En este proyecto de trabajo de grado, se desarrolló una aplicación web con información para atender preguntas frecuentes y consultas acerca de algunos procesos administrativos que puedan tener los estudiantes de ingeniería de sistemas de la sede Tuluá, con el apoyo de un asistente virtual (chatbot) para la resolución de dudas acerca de la información requerida, con el fin de reducir el tiempo que usa el personal administrativo en la atención de estos asuntos, incrementando la productividad de los mismos y a su vez dar una respuesta oportuna a dudas o preguntas frecuentes de los alumnos evitando que se desplacen a la oficina o en contra parte, que envíen correos que debido al gran volumen de estos, la respuesta tardará algo de tiempo en llegar. En el desarrollo del proyecto se utilizó inteligencia artificial (IA) para la creación del chatbot incorporando técnicas de procesamiento de lenguaje natural (PLN) para que los estudiantes tengan una interacción fluida y facilidad para dar respuesta a sus cuestionamientos. Además, se adoptó un enfoque web, considerando que actualmente las personas utilizan cada vez más dispositivos inteligentes. Desarrollar una aplicación nativa para cada plataforma puede ser una tarea ardua. Este problema puede ser mitigado significativamente mediante el uso de tecnologías web, ya que permiten que la aplicación sea accesible desde una amplia gama de dispositivos con el único requisito de contar con un navegador web compatible.</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025S17</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DISEÑO E IMPLEMENTACIÓN DE UN LAUNCHER ANDROID ENFOCADO A COMBATIR LA PROCRASTINACIÓN POR EL USO EXCESIVO DEL SMARTPHONE EN ESTUDIANTES DE PREGRADO DE LA UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mitigar distracciones, procrastinación, smartphone, telefonos android, launcher.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Los estudiantes universitarios que hacen un uso excesivo y/o inadecuado del smartphone tienen un menor rendimiento académico e insatisfacción al no gestionar adecuadamente su tiempo e incumplir los plazos de sus actividades pendientes. Dado que el ecosistema de los teléfonos móviles y sus aplicaciones incentiva a pasar el mayor tiempo posible usándolos, se propone desarrollar una pantalla de inicio (launcher) para teléfonos Android que apunte a reducir la procrastinación mediante una interfaz mínimamente llamativa, a mitigar las distracciones y a gestionar mejor el tiempo invertido dentro de las aplicaciones, principalmente en horarios donde se requiera total disposición a una actividad concreta.</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2025S18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SISTEMA DE OPTIMIZACIÓN DE LA PROGRAMACIÓN ACADÉMICA PARA LA SECCIONAL BUGA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Sistema de Optimización, programación academica, gestión horaria.</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>El problema estudiado es la gestión ineficiente de horarios y recursos en instituciones educativas, lo que puede provocar conflictos de horarios y una utilización subóptima de los recursos disponibles. Se estudia con el fin de mejorar la eficiencia y la organización en la programación académica. El sistema utiliza algoritmos avanzados para optimizar la distribución de clases, estos algoritmos tienen en cuenta múltiples factores, como la disponibilidad de docentes, requerimientos de asignaturas y características de los salones. Proporcionan una programación académica óptima, minimizando conflictos de horarios y maximizando la utilización de recursos disponibles, a través de una interfaz que permita a los administradores ingresar información relevante. Los resultados obtenidos demuestran que el Sistema de Optimización de Programación Académica es eficaz para mejorar la gestión de horarios y recursos en instituciones educativas. Esto significa que se puede lograr una distribución equitativa de las clases y una utilización más eficiente de los recursos disponibles, lo que contribuye a un funcionamiento más fluido y productivo.</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2025S19</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE SOFTWARE USANDO LA GAMIFICACIÓN PARA El APOYO DEL APRENDIZAJE EN LA ASIGNATURA DE CIENCIAS SOCIALES Y EN LA CULTURA GENERAL COLOMBIANA EN NIÑOS DE 5TO GRADO DE PRIMARIA</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Videojuegos, gamificación, ciencias sociales, aprendizaje.</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Este trabajo de grado presenta el desarrollo de un prototipo de videojuego junto a elementos de gamificación, aplicado en el área de Ciencias Sociales y en las competencias de cultura general colombiana, diseñado específicamente para estudiantes de quinto grado de primaria. La propuesta surge como respuesta a la necesidad de generar herramientas innovadoras que despierten el interés de los niños y apoyen su aprendizaje. Durante la etapa de investigación, se realizó un proceso de recopilación y análisis de contenidos educativos a partir de fuentes confiables, planes de estudio oficiales y materiales de libre acceso en línea, ante la dificultad de obtener insumos directamente de las instituciones educativas. Esto permitió construir diálogos, escenarios y dinámicas representativas de cuatro regiones del país: Caribe, Pacífica, Orinoquía y Amazonía. La implementación técnica se llevó a cabo utilizando un motor gráfico apoyado en herramientas para el modelado 3D, las animaciones de personajes, la generación de texturas y bibliotecas de sonido de libre uso. El videojuego fue diseñado con una estructura modular de misiones, cada una con objetivos específicos y personajes interactivos que fomentan la exploración. La fase de pruebas incluyó la aplicación del prototipo en un grupo real de estudiantes, mediante observación directa y entrevistas estructuradas tanto a los niños como a su docente. Los resultados muestran un alto nivel de motivación, participación activa y comprensión temática por parte de los estudiantes, validando la efectividad del enfoque lúdico para el aprendizaje de las Ciencias Sociales y la cultura general. Este proyecto demostró la viabilidad técnica y pedagógica de integrar el desarrollo de software con la educación primaria, proponiendo un modelo replicable que puede ser ampliado y mejorado en futuras investigaciones. Así, se reafirma el potencial de los videojuegos como herramientas educativas valiosas en contextos escolares</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2025S20</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DESARROLLO DE UN PROTOTIPO DE APLICACIÓN WEB PARA LA IMPLEMENTACIÓN DE UN SISTEMA DE RECOMENDACIÓN DE ROPA BASADO EN EL BIENESTAR EMOCIONAL DEL USUARIO MEDIANTE LA INTEGRACIÓN DE LA ECONOMÍA CONDUCTUAL</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Clothing recommendation system, Prototype web application, Human computer interaction, user interfaces, Sentiment analysis.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>En la ingeniería de sistemas, el diseño de aplicaciones web suele centrarse en aspectos técnicos, dejando de lado las emociones del usuario. Esta limitación es particularmente evidente en las plataformas de recomendación de ropa, donde la falta de empatía genera experiencias impersonales y desconectadas emocionalmente. Como resultado, se afecta la toma de decisiones, la fidelización y la satisfacción de los usuarios. Este trabajo de grado propuso el desarrollo de un prototipo de aplicación web que incorpora el análisis emocional del usuario y principios de la Economía Conductual para ofrecer recomendaciones de ropa más humanas, personalizadas y emocionalmente relevantes. El objetivo no fue solo facilitar la elección de una prenda, sino también atender el estado emocional de cada individuo y reconocer su influencia en la interacción con la tecnología. La propuesta se construyó desde un enfoque interdisciplinario, integrando psicología del usuario, interacción humano-computadora y bienestar digital. Se trabajó con conceptos como inteligencia emocional, modelado de estados afectivos y toma de decisiones influenciada por emociones. Los resultados del prototipo demostraron que incluir elementos emocionales mejora la experiencia digital, fomenta la personalización y permite construir plataformas más sensibles y alineadas con las necesidades reales del usuario. Este enfoque contribuye a una visión más humana de la tecnología y plantea nuevas posibilidades para el diseño digital en la moda y otros sectores.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2025S21</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>PROTOTIPO DE SISTEMA DE DETECCION TEMPRANA DE SOFTWARE MALINTENCIONADO POR MEDIO DE COMPORTAMIENTOS ANÓMALOS EN WINDOWS 10</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Ransomware de cifrado, ciberseguridad, ciberataque, integridad de datos.</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Este proyecto se realizó con el objetivo de desarrollar un prototipo de sistema para la detección temprana de comportamientos anómalos en el sistema operativo Windows 10, con el fin de prevenir posibles ataques de ransomware de cifrado y la pérdida de datos que estos conllevan. La justificación de este trabajo radica en la necesidad de herramientas que permitan identificar patrones de comportamiento sospechosos en sistemas informáticos, específicamente en Windows 10, lo que posibilitará recolectar la información necesaria para detectar cuándo se está ejecutando un ataque de ransomware y desplegar una respuesta efectiva en el sistema operativo, reduciendo significativamente el riesgo de pérdida de información. Finalmente, se consiguió desarrollar un prototipo de detección funcional con un alto nivel de asertividad en la detección de comportamientos anómalos por medio de la aplicación de puntaje por entropía, lo cuál cumple con los objetivos planteados.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>seguimiento_2025</t>
         </is>
       </c>
     </row>
